--- a/Mediciones/RNA/Serpiente/RUN2_Serpiente_2NO.xlsx
+++ b/Mediciones/RNA/Serpiente/RUN2_Serpiente_2NO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\RNA\Serpiente\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2F21EB-13FB-4837-9975-48B364460F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E91B5CF-AA1D-48FA-A66F-63DE42778A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -308,6 +308,9 @@
     <t>sensors_n_now</t>
   </si>
   <si>
+    <t>RNA</t>
+  </si>
+  <si>
     <t>{
   "timestamp": "2026-07-18T21:44:50",
   "bounds": {
@@ -318,7 +321,7 @@
   },
   "serial": {
     "port": "COM7",
-    "baud": "460800",
+    "baud": "115200",
     "eol": "LF",
     "send_enabled": true
   },
@@ -409,9 +412,6 @@
   "run_id": "R20260718_214450",
   "repetition": 1
 }</t>
-  </si>
-  <si>
-    <t>RNA</t>
   </si>
 </sst>
 </file>
@@ -767,7 +767,7 @@
     </row>
     <row r="2" spans="1:1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D2">
         <v>0.3255131964809384</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D3">
         <v>0.3255131964809384</v>
@@ -975,7 +975,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D4">
         <v>0.3255131964809384</v>
@@ -1028,7 +1028,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5">
         <v>0.3255131964809384</v>
@@ -1081,7 +1081,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6">
         <v>0.3255131964809384</v>
@@ -1134,7 +1134,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7">
         <v>0.3255131964809384</v>
@@ -1187,7 +1187,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8">
         <v>0.3255131964809384</v>
@@ -1240,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9">
         <v>0.3255131964809384</v>
@@ -1293,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D10">
         <v>0.3255131964809384</v>
@@ -1346,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11">
         <v>0.3255131964809384</v>
@@ -1399,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12">
         <v>0.3255131964809384</v>
@@ -1452,7 +1452,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13">
         <v>0.3255131964809384</v>
@@ -1505,7 +1505,7 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D14">
         <v>0.3255131964809384</v>
@@ -1558,7 +1558,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15">
         <v>0.3255131964809384</v>
@@ -1611,7 +1611,7 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16">
         <v>0.3255131964809384</v>
@@ -1664,7 +1664,7 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17">
         <v>0.3255131964809384</v>
@@ -1717,7 +1717,7 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18">
         <v>0.3255131964809384</v>
@@ -1770,7 +1770,7 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19">
         <v>0.3255131964809384</v>
@@ -1823,7 +1823,7 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20">
         <v>0.3255131964809384</v>
@@ -1876,7 +1876,7 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21">
         <v>0.3255131964809384</v>
@@ -1929,7 +1929,7 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22">
         <v>0.3255131964809384</v>
@@ -1982,7 +1982,7 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23">
         <v>0.3255131964809384</v>
@@ -2035,7 +2035,7 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24">
         <v>0.3255131964809384</v>
@@ -2088,7 +2088,7 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25">
         <v>0.3255131964809384</v>
@@ -2141,7 +2141,7 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26">
         <v>0.97485774086369958</v>
@@ -2194,7 +2194,7 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27">
         <v>0.97485774086369958</v>
@@ -2247,7 +2247,7 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28">
         <v>0.97485774086370003</v>
@@ -2300,7 +2300,7 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29">
         <v>0.97485774086369958</v>
@@ -2353,7 +2353,7 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D30">
         <v>0.97485774086369958</v>
@@ -2406,7 +2406,7 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31">
         <v>0.97485774086369958</v>
@@ -2459,7 +2459,7 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32">
         <v>0.97485774086369958</v>
@@ -2512,7 +2512,7 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33">
         <v>0.97485774086369958</v>
@@ -2565,7 +2565,7 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D34">
         <v>0.97485774086369958</v>
@@ -2618,7 +2618,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35">
         <v>0.97485774086369958</v>
@@ -2671,7 +2671,7 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36">
         <v>0.97485774086369958</v>
@@ -2724,7 +2724,7 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D37">
         <v>0.97485774086369958</v>
@@ -2777,7 +2777,7 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38">
         <v>0.97485774086369958</v>
@@ -2830,7 +2830,7 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D39">
         <v>0.97485774086369958</v>
@@ -2883,7 +2883,7 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D40">
         <v>0.97485774086369958</v>
@@ -2936,7 +2936,7 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D41">
         <v>0.97485774086369958</v>
@@ -2989,7 +2989,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42">
         <v>0.97485774086369958</v>
@@ -3042,7 +3042,7 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D43">
         <v>0.97485774086369958</v>
@@ -3095,7 +3095,7 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D44">
         <v>0.97485774086369958</v>
@@ -3148,7 +3148,7 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D45">
         <v>0.97485774086369958</v>
@@ -3201,7 +3201,7 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D46">
         <v>0.97485774086369958</v>
@@ -3254,7 +3254,7 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D47">
         <v>0.97485774086369958</v>
@@ -3307,7 +3307,7 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D48">
         <v>0.97485774086369958</v>
@@ -3360,7 +3360,7 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D49">
         <v>0.97485774086369958</v>
@@ -3413,7 +3413,7 @@
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D50">
         <v>0.97485774086369958</v>
@@ -3466,7 +3466,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D51">
         <v>0.97485774086369958</v>
@@ -3519,7 +3519,7 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52">
         <v>0.97485774086369958</v>
@@ -3572,7 +3572,7 @@
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D53">
         <v>0.97485774086369958</v>
@@ -3625,7 +3625,7 @@
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D54">
         <v>0.97485774086369958</v>
@@ -3678,7 +3678,7 @@
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D55">
         <v>0.97485774086369958</v>
@@ -3731,7 +3731,7 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D56">
         <v>0.97485774086369958</v>
@@ -3784,7 +3784,7 @@
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D57">
         <v>0.97485774086369958</v>
@@ -3837,7 +3837,7 @@
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D58">
         <v>0.97485774086369958</v>
@@ -3890,7 +3890,7 @@
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D59">
         <v>0.97485774086369958</v>
@@ -3943,7 +3943,7 @@
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D60">
         <v>0.97485774086369958</v>
@@ -3996,7 +3996,7 @@
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61">
         <v>0.97485774086369958</v>
@@ -4049,7 +4049,7 @@
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D62">
         <v>0.97485774086369958</v>
@@ -4102,7 +4102,7 @@
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D63">
         <v>0.97485774086369958</v>
@@ -4155,7 +4155,7 @@
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D64">
         <v>0.97485774086369958</v>
@@ -4208,7 +4208,7 @@
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D65">
         <v>0.97485774086369958</v>
@@ -4261,7 +4261,7 @@
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66">
         <v>0.97485774086369958</v>
@@ -4314,7 +4314,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D67">
         <v>0.97485774086369958</v>
@@ -4367,7 +4367,7 @@
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D68">
         <v>0.97485774086369958</v>
@@ -4420,7 +4420,7 @@
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D69">
         <v>0.97485774086369958</v>
@@ -4473,7 +4473,7 @@
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D70">
         <v>0.97485774086369958</v>
@@ -4526,7 +4526,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D71">
         <v>0.97485774086369958</v>
@@ -4579,7 +4579,7 @@
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D72">
         <v>0.97485774086369958</v>
@@ -4632,7 +4632,7 @@
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D73">
         <v>0.97485774086369958</v>
@@ -4685,7 +4685,7 @@
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D74">
         <v>0.97485774086369958</v>
@@ -4738,7 +4738,7 @@
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D75">
         <v>0.97485774086369958</v>
@@ -4791,7 +4791,7 @@
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D76">
         <v>0.97485774086369958</v>
@@ -4844,7 +4844,7 @@
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D77">
         <v>0.97485774086369958</v>
@@ -4897,7 +4897,7 @@
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D78">
         <v>0.97485774086369958</v>
@@ -4950,7 +4950,7 @@
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D79">
         <v>0.97485774086369958</v>
@@ -5003,7 +5003,7 @@
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D80">
         <v>0.97485774086369958</v>
@@ -5056,7 +5056,7 @@
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D81">
         <v>0.97485774086369958</v>
@@ -5109,7 +5109,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D82">
         <v>0.97485774086369958</v>
@@ -5162,7 +5162,7 @@
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D83">
         <v>0.97485774086369958</v>
@@ -5215,7 +5215,7 @@
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D84">
         <v>0.97485774086369958</v>
@@ -5268,7 +5268,7 @@
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D85">
         <v>0.97485774086369958</v>
@@ -5321,7 +5321,7 @@
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D86">
         <v>0.97485774086369958</v>
@@ -5374,7 +5374,7 @@
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D87">
         <v>0.97485774086369958</v>
@@ -5427,7 +5427,7 @@
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D88">
         <v>0.97485774086369958</v>
@@ -5480,7 +5480,7 @@
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D89">
         <v>0.97485774086369958</v>
@@ -5533,7 +5533,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D90">
         <v>0.97485774086369958</v>
@@ -5586,7 +5586,7 @@
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D91">
         <v>0.97485774086369958</v>
@@ -5639,7 +5639,7 @@
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D92">
         <v>0.97485774086369958</v>
@@ -5692,7 +5692,7 @@
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D93">
         <v>0.97485774086369958</v>
@@ -5745,7 +5745,7 @@
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D94">
         <v>0.97485774086369958</v>
@@ -5798,7 +5798,7 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D95">
         <v>0.97485774086369958</v>
@@ -5851,7 +5851,7 @@
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D96">
         <v>0.97485774086369958</v>
@@ -5904,7 +5904,7 @@
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D97">
         <v>0.97485774086369958</v>
@@ -5957,7 +5957,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D98">
         <v>0.97485774086369958</v>
@@ -6010,7 +6010,7 @@
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D99">
         <v>0.97485774086369958</v>
@@ -6063,7 +6063,7 @@
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D100">
         <v>0.97485774086369958</v>
@@ -6116,7 +6116,7 @@
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D101">
         <v>0.97485774086369958</v>
@@ -6169,7 +6169,7 @@
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D102">
         <v>0.97485774086369958</v>
@@ -6222,7 +6222,7 @@
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D103">
         <v>0.97485774086369958</v>
@@ -6275,7 +6275,7 @@
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D104">
         <v>0.97485774086369958</v>
@@ -6328,7 +6328,7 @@
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D105">
         <v>0.97485774086369958</v>
@@ -6381,7 +6381,7 @@
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D106">
         <v>0.97485774086369958</v>
@@ -6434,7 +6434,7 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D107">
         <v>0.97485774086369958</v>
@@ -6487,7 +6487,7 @@
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D108">
         <v>0.97485774086369958</v>
@@ -6540,7 +6540,7 @@
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D109">
         <v>0.97485774086369958</v>
@@ -6593,7 +6593,7 @@
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D110">
         <v>0.97485774086369958</v>
@@ -6646,7 +6646,7 @@
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D111">
         <v>0.97485774086369958</v>
@@ -6699,7 +6699,7 @@
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D112">
         <v>0.97485774086369958</v>
@@ -6752,7 +6752,7 @@
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D113">
         <v>0.97485774086369958</v>
@@ -6805,7 +6805,7 @@
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D114">
         <v>0.97485774086369958</v>
@@ -6858,7 +6858,7 @@
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D115">
         <v>0.97485774086369958</v>
@@ -6911,7 +6911,7 @@
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D116">
         <v>0.97485774086369958</v>
@@ -6964,7 +6964,7 @@
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D117">
         <v>0.97485774086369958</v>
@@ -7017,7 +7017,7 @@
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D118">
         <v>0.97485774086369958</v>
@@ -7070,7 +7070,7 @@
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D119">
         <v>0.97485774086369958</v>
@@ -7123,7 +7123,7 @@
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D120">
         <v>0.97485774086369958</v>
@@ -7176,7 +7176,7 @@
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D121">
         <v>0.97485774086369958</v>
@@ -10688,7 +10688,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
